--- a/DataTables/DetailText/剧情/006药商来访.xlsx
+++ b/DataTables/DetailText/剧情/006药商来访.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC243823-785F-4D29-AB40-1231970EB0EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A68231-41F1-43E7-B7F6-9A4082A6EBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="51">
   <si>
     <t>StoryID</t>
   </si>
@@ -76,14 +76,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>res://Assets/Background/</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>mid</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Hide</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -152,11 +144,143 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>要上来访</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>人参</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>贾荃</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>006/006.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生意兴隆啊老板，嘿嘿嘿。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>李东璧</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敢问您是？(哎呀我的妈，吓我一跳，这人什么时候进来的...)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>久闻久闻，今日来小馆是所为何事呀？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>在下贾荃，是做药材生意的，在湖广省小有一点名气，嘿嘿嘿。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>呃，呵呵，今日是想找李神医谈一桩好生意。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哦？愿闻其详。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>小可上个月进了一批人参，想请李兄在医馆帮忙出货。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>而是小馆平时接待的病患多是平常百姓，人参这种名贵药材用量是不多的。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>李兄此言差矣，人参是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>补药，是病就得补。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>像那种</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头疼脑热的小病您也给加一点，这量不就有了嘛。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>按病开方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>岂能胡乱加药？</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>不白加，每斤人参我给您一两白银的提成，怎么样，是桩好生意吧。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>您还是请回吧，陈皮，送客。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>陈皮</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mid</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>贾老板，您这边请。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哼，真是不知好歹。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>药商来访</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -283,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -331,6 +455,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -638,66 +765,66 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="K1" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="15" t="s">
+      <c r="P1" s="15" t="s">
         <v>18</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1">
         <v>2</v>
@@ -705,7 +832,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="16"/>
       <c r="I2" s="17" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -787,7 +914,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
@@ -818,7 +945,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>10</v>
@@ -834,16 +961,20 @@
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="17" t="s">
+        <v>31</v>
+      </c>
       <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
       <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
@@ -852,14 +983,18 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="17" t="s">
+        <v>34</v>
+      </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="1"/>
+      <c r="H3" s="17" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
@@ -868,14 +1003,18 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="7" t="s">
-        <v>12</v>
+      <c r="C4" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="1"/>
+      <c r="H4" s="17" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
@@ -884,36 +1023,218 @@
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="17" t="s">
+        <v>34</v>
+      </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="1"/>
+      <c r="H5" s="17" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="2"/>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="1"/>
+      <c r="H6" s="17" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2"/>
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="H7" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="18" t="s">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/006药商来访.xlsx
+++ b/DataTables/DetailText/剧情/006药商来访.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A68231-41F1-43E7-B7F6-9A4082A6EBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596204A2-6A50-4956-83ED-FD8CAB8BAC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -276,11 +276,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>哼，真是不知好歹。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>药商来访</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哼，不知好歹。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -815,7 +815,7 @@
         <v>29</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>19</v>
@@ -826,9 +826,7 @@
       <c r="E2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="1">
-        <v>2</v>
-      </c>
+      <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="16"/>
       <c r="I2" s="17" t="s">
@@ -965,7 +963,7 @@
         <v>31</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
@@ -987,7 +985,7 @@
         <v>34</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="7"/>
@@ -1007,7 +1005,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="7"/>
@@ -1027,7 +1025,7 @@
         <v>34</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -1047,7 +1045,7 @@
         <v>31</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -1067,7 +1065,7 @@
         <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -1087,7 +1085,7 @@
         <v>31</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -1107,7 +1105,7 @@
         <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -1127,7 +1125,7 @@
         <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -1147,7 +1145,7 @@
         <v>34</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1167,7 +1165,7 @@
         <v>31</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -1187,7 +1185,7 @@
         <v>34</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1227,13 +1225,13 @@
         <v>31</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/006药商来访.xlsx
+++ b/DataTables/DetailText/剧情/006药商来访.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596204A2-6A50-4956-83ED-FD8CAB8BAC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BDC707-4495-4645-B4F4-0C58FE01698C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -20,17 +20,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -197,10 +186,6 @@
   </si>
   <si>
     <t>小可上个月进了一批人参，想请李兄在医馆帮忙出货。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>而是小馆平时接待的病患多是平常百姓，人参这种名贵药材用量是不多的。</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -283,16 +268,20 @@
     <t>哼，不知好歹。</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>小馆平时接待的病患多是平常百姓，人参这种名贵药材用量是不多的。</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -306,7 +295,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -327,7 +316,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -461,7 +450,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -740,27 +729,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -810,12 +799,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="18.75">
       <c r="A2" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>19</v>
@@ -844,64 +833,64 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="9"/>
       <c r="H3" s="13"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="18.75">
       <c r="C4" s="9"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="18.75">
       <c r="C5" s="9"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="18.75">
       <c r="C6" s="9"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="18.75">
       <c r="C7" s="9"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="18.75">
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="18.75">
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="18.75">
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="18.75">
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="18.75">
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="18.75">
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="18.75">
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="18.75">
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="18.75">
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8" ht="18.75">
       <c r="H17" s="13"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8" ht="18.75">
       <c r="H18" s="13"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8" ht="18.75">
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8" ht="18.75">
       <c r="H20" s="13"/>
     </row>
   </sheetData>
@@ -913,20 +902,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -952,7 +941,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -974,7 +963,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -994,7 +983,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1014,7 +1003,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1034,7 +1023,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1054,7 +1043,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1074,7 +1063,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1094,7 +1083,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1111,10 +1100,10 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1131,10 +1120,10 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1151,10 +1140,10 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1171,10 +1160,10 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1191,10 +1180,10 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1202,19 +1191,19 @@
         <v>6</v>
       </c>
       <c r="C14" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1231,7 +1220,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/006药商来访.xlsx
+++ b/DataTables/DetailText/剧情/006药商来访.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BDC707-4495-4645-B4F4-0C58FE01698C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF35D308-1F1A-4E23-B721-24454F7A78B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -20,6 +20,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -166,10 +177,6 @@
   </si>
   <si>
     <t>敢问您是？(哎呀我的妈，吓我一跳，这人什么时候进来的...)</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>久闻久闻，今日来小馆是所为何事呀？</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -272,16 +279,20 @@
     <t>小馆平时接待的病患多是平常百姓，人参这种名贵药材用量是不多的。</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>久闻久闻，不知今日来小馆所为何事？</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -295,7 +306,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -316,7 +327,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -450,7 +461,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -729,27 +740,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -799,12 +810,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="18.75">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>19</v>
@@ -833,64 +844,64 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="9"/>
       <c r="H3" s="13"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="9"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:16" ht="18.75">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="9"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:16" ht="18.75">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C6" s="9"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C7" s="9"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:16" ht="18.75">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:16" ht="18.75">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:16" ht="18.75">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:16" ht="18.75">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:16" ht="18.75">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:16" ht="18.75">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:16" ht="18.75">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:16" ht="18.75">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H17" s="13"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H18" s="13"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="8:8" ht="18.75">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H20" s="13"/>
     </row>
   </sheetData>
@@ -902,20 +913,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -941,7 +952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -963,7 +974,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -983,7 +994,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1000,10 +1011,10 @@
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
       <c r="H4" s="17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1020,10 +1031,10 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1040,10 +1051,10 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1060,10 +1071,10 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1080,10 +1091,10 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1100,10 +1111,10 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="18" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1120,10 +1131,10 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1140,10 +1151,10 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1160,10 +1171,10 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1180,10 +1191,10 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1191,19 +1202,19 @@
         <v>6</v>
       </c>
       <c r="C14" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1220,7 +1231,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/006药商来访.xlsx
+++ b/DataTables/DetailText/剧情/006药商来访.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF35D308-1F1A-4E23-B721-24454F7A78B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76C64A7-FF5D-400D-B37B-6C89CBB18CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -20,17 +20,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -288,11 +277,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -306,7 +295,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -327,7 +316,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -461,7 +450,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -740,27 +729,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -810,7 +799,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16">
       <c r="A2" s="16" t="s">
         <v>29</v>
       </c>
@@ -844,64 +833,64 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="9"/>
       <c r="H3" s="13"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="18.75">
       <c r="C4" s="9"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="18.75">
       <c r="C5" s="9"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="18.75">
       <c r="C6" s="9"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="18.75">
       <c r="C7" s="9"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="18.75">
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="18.75">
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="18.75">
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="18.75">
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="18.75">
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="18.75">
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="18.75">
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="18.75">
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="18.75">
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8" ht="18.75">
       <c r="H17" s="13"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8" ht="18.75">
       <c r="H18" s="13"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8" ht="18.75">
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8" ht="18.75">
       <c r="H20" s="13"/>
     </row>
   </sheetData>
@@ -913,20 +902,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -952,7 +941,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -974,7 +963,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -994,7 +983,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1014,7 +1003,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1034,7 +1023,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1054,7 +1043,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1074,7 +1063,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1094,7 +1083,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1114,7 +1103,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1134,7 +1123,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1154,7 +1143,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1174,7 +1163,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1194,7 +1183,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1214,7 +1203,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8">
       <c r="A15" s="3">
         <v>14</v>
       </c>

--- a/DataTables/DetailText/剧情/006药商来访.xlsx
+++ b/DataTables/DetailText/剧情/006药商来访.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76C64A7-FF5D-400D-B37B-6C89CBB18CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6D79A0-87FC-4352-A1E4-D49DA2177738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3045" yWindow="2670" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -138,22 +138,6 @@
   </si>
   <si>
     <t>贾荃</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>res://Assets/Background/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>006/006.png</t>
-    </r>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -271,6 +255,9 @@
   <si>
     <t>久闻久闻，不知今日来小馆所为何事？</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>current_scene</t>
   </si>
 </sst>
 </file>
@@ -804,7 +791,7 @@
         <v>29</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>19</v>
@@ -838,59 +825,59 @@
       <c r="H3" s="13"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75">
+    <row r="4" spans="1:16">
       <c r="C4" s="9"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:16" ht="18.75">
+    <row r="5" spans="1:16">
       <c r="C5" s="9"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:16" ht="18.75">
+    <row r="6" spans="1:16">
       <c r="C6" s="9"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75">
+    <row r="7" spans="1:16">
       <c r="C7" s="9"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:16" ht="18.75">
+    <row r="8" spans="1:16">
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:16" ht="18.75">
+    <row r="9" spans="1:16">
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:16" ht="18.75">
+    <row r="10" spans="1:16">
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:16" ht="18.75">
+    <row r="11" spans="1:16">
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:16" ht="18.75">
+    <row r="12" spans="1:16">
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75">
+    <row r="13" spans="1:16">
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:16" ht="18.75">
+    <row r="14" spans="1:16">
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:16" ht="18.75">
+    <row r="15" spans="1:16">
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:16" ht="18.75">
+    <row r="16" spans="1:16">
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8">
       <c r="H17" s="13"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8">
       <c r="H18" s="13"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8">
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="8:8" ht="18.75">
+    <row r="20" spans="8:8">
       <c r="H20" s="13"/>
     </row>
   </sheetData>
@@ -957,10 +944,10 @@
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
       <c r="G2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="17" t="s">
         <v>32</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -971,7 +958,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>9</v>
@@ -980,7 +967,7 @@
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
       <c r="H3" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1000,7 +987,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
       <c r="H4" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1011,7 +998,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
@@ -1020,7 +1007,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1040,7 +1027,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1051,7 +1038,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>9</v>
@@ -1060,7 +1047,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1080,7 +1067,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1091,7 +1078,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
@@ -1100,7 +1087,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1120,7 +1107,7 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1131,7 +1118,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>9</v>
@@ -1140,7 +1127,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1160,7 +1147,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1171,7 +1158,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>9</v>
@@ -1180,7 +1167,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1191,16 +1178,16 @@
         <v>6</v>
       </c>
       <c r="C14" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1220,7 +1207,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/006药商来访.xlsx
+++ b/DataTables/DetailText/剧情/006药商来访.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6D79A0-87FC-4352-A1E4-D49DA2177738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138A775B-FA92-4578-9830-6D7BFFA90A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3045" yWindow="2670" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -146,10 +157,6 @@
   </si>
   <si>
     <t>李东璧</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>敢问您是？(哎呀我的妈，吓我一跳，这人什么时候进来的...)</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -259,16 +266,20 @@
   <si>
     <t>current_scene</t>
   </si>
+  <si>
+    <t>敢问您是？(这人什么时候进来的...)</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -282,7 +293,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -303,7 +314,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -437,7 +448,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -716,27 +727,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -786,12 +797,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>19</v>
@@ -820,64 +831,64 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="9"/>
       <c r="H3" s="13"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="9"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="9"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C6" s="9"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C7" s="9"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="8:8">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H17" s="13"/>
     </row>
-    <row r="18" spans="8:8">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H18" s="13"/>
     </row>
-    <row r="19" spans="8:8">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="8:8">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H20" s="13"/>
     </row>
   </sheetData>
@@ -889,20 +900,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -928,7 +939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -944,13 +955,13 @@
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
       <c r="G2" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -967,10 +978,10 @@
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
       <c r="H3" s="17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -987,10 +998,10 @@
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
       <c r="H4" s="17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1007,10 +1018,10 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1027,10 +1038,10 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1047,10 +1058,10 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1067,10 +1078,10 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1087,10 +1098,10 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1107,10 +1118,10 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1127,10 +1138,10 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1147,10 +1158,10 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1167,10 +1178,10 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="18" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1178,19 +1189,19 @@
         <v>6</v>
       </c>
       <c r="C14" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>44</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1207,7 +1218,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/006药商来访.xlsx
+++ b/DataTables/DetailText/剧情/006药商来访.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138A775B-FA92-4578-9830-6D7BFFA90A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384A615D-8F74-4485-AEB7-34D7559B9DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="51">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="54">
   <si>
     <t>LineIndex</t>
   </si>
@@ -80,64 +66,13 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
   </si>
   <si>
-    <t>scene_enter</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>clinic</t>
-  </si>
-  <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>006</t>
@@ -270,16 +205,101 @@
     <t>敢问您是？(这人什么时候进来的...)</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -293,7 +313,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -314,7 +334,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -329,13 +349,27 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Noto Sans JP"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -350,20 +384,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -394,7 +430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -417,26 +453,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -446,9 +471,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -726,173 +782,199 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:20" s="21" customFormat="1">
+      <c r="A1" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="L1" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="O1" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="P1" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="R1" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="S1" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:20" s="21" customFormat="1">
+      <c r="A2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="12" t="s">
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A2" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="1" t="b">
+      <c r="K2" s="23"/>
+      <c r="L2" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="22"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C3" s="9"/>
-      <c r="H3" s="13"/>
-      <c r="O3" s="10"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C4" s="9"/>
-      <c r="H4" s="13"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C5" s="9"/>
-      <c r="H5" s="13"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C6" s="9"/>
-      <c r="H6" s="13"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C7" s="9"/>
-      <c r="H7" s="13"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H8" s="13"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H9" s="13"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H10" s="13"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H11" s="13"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H12" s="13"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H14" s="13"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H15" s="13"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H16" s="13"/>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H17" s="13"/>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H18" s="13"/>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H19" s="13"/>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H20" s="13"/>
+      <c r="T2" s="24"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="8"/>
+      <c r="H3" s="10"/>
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="C4" s="8"/>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="C5" s="8"/>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="C6" s="8"/>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="C7" s="8"/>
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="H16" s="10"/>
+    </row>
+    <row r="17" spans="8:8">
+      <c r="H17" s="10"/>
+    </row>
+    <row r="18" spans="8:8">
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="8:8">
+      <c r="H19" s="10"/>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{B09566C9-B235-46C3-8F5F-3A9B349D3DF5}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{4044AE2E-E63F-4418-B4F6-B4C38E1EAEFD}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{0ADEFCAA-4ECC-467B-B7DC-6DC9600461B1}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{CAF5A14D-6466-408A-9FA9-516229153713}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{14473630-CD13-4F2A-B5B2-BD4BBCA61D12}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -900,325 +982,325 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>31</v>
+        <v>5</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
       <c r="G2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>33</v>
+        <v>5</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H3" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>31</v>
+        <v>5</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H4" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>33</v>
+        <v>5</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H5" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>31</v>
+        <v>5</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H6" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>33</v>
+        <v>5</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H7" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>31</v>
+        <v>5</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H8" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>33</v>
+        <v>5</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H9" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>31</v>
+        <v>5</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>33</v>
+        <v>5</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>31</v>
+        <v>5</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H12" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>33</v>
+        <v>5</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H13" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>42</v>
+        <v>5</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H14" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>31</v>
+        <v>5</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="18" t="s">
-        <v>46</v>
+      <c r="H15" s="13" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/006药商来访.xlsx
+++ b/DataTables/DetailText/剧情/006药商来访.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384A615D-8F74-4485-AEB7-34D7559B9DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65AA0DC2-4629-41B9-8575-40C0C99EBF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2768" yWindow="4057" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -877,10 +877,10 @@
       <c r="F2" s="23"/>
       <c r="G2" s="23"/>
       <c r="H2" s="23"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="12" t="s">
+      <c r="I2" s="12" t="s">
         <v>15</v>
       </c>
+      <c r="J2" s="12"/>
       <c r="K2" s="23"/>
       <c r="L2" s="23" t="s">
         <v>13</v>

--- a/DataTables/DetailText/剧情/006药商来访.xlsx
+++ b/DataTables/DetailText/剧情/006药商来访.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65AA0DC2-4629-41B9-8575-40C0C99EBF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04AF8C67-7828-4D30-9DD1-DE0F06CC1F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2768" yWindow="4057" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19740" yWindow="5400" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="55">
   <si>
     <t>LineIndex</t>
   </si>
@@ -290,6 +301,10 @@
     <t>奖励心得</t>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -299,7 +314,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -313,7 +328,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -334,7 +349,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -430,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -502,9 +517,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -783,24 +801,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1">
+    <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A1" s="14" t="s">
         <v>36</v>
       </c>
@@ -862,7 +880,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="21" customFormat="1">
+    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A2" s="11" t="s">
         <v>14</v>
       </c>
@@ -981,21 +999,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="92.125" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1020,8 +1038,11 @@
       <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1042,8 +1063,9 @@
       <c r="H2" s="12" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1062,8 +1084,9 @@
       <c r="H3" s="12" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1082,8 +1105,9 @@
       <c r="H4" s="12" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1102,8 +1126,9 @@
       <c r="H5" s="12" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1122,8 +1147,9 @@
       <c r="H6" s="12" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1142,8 +1168,9 @@
       <c r="H7" s="13" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1162,8 +1189,9 @@
       <c r="H8" s="13" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1182,8 +1210,9 @@
       <c r="H9" s="13" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1202,8 +1231,9 @@
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1222,8 +1252,9 @@
       <c r="H11" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1242,8 +1273,9 @@
       <c r="H12" s="13" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1262,8 +1294,9 @@
       <c r="H13" s="13" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1282,8 +1315,9 @@
       <c r="H14" s="13" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1302,6 +1336,7 @@
       <c r="H15" s="13" t="s">
         <v>31</v>
       </c>
+      <c r="I15" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
